--- a/tests/fixtures/table-refs-sample.xlsx
+++ b/tests/fixtures/table-refs-sample.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zeroa\AppData\Local\Temp\claude\C--WINDOWS-System32-WindowsPowerShell-v1-0\724980bf-bf5e-4112-8110-90c2ad7ecebc\scratchpad\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url=""/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{78740364-DE9D-4662-8BA8-F17960E64924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
